--- a/AAII_Financials/Quarterly/CULL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CULL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
   <si>
     <t>CULL</t>
   </si>
@@ -656,176 +656,180 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E8" s="3">
         <v>4800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3300</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
@@ -838,8 +842,8 @@
       <c r="R8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -880,8 +884,11 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -972,8 +979,11 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1074,11 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,8 +1394,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,44 +1523,45 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1000</v>
-      </c>
-      <c r="E17" s="3">
-        <v>800</v>
       </c>
       <c r="F17" s="3">
         <v>800</v>
       </c>
       <c r="G17" s="3">
+        <v>800</v>
+      </c>
+      <c r="H17" s="3">
         <v>400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>300</v>
-      </c>
-      <c r="J17" s="3">
-        <v>400</v>
       </c>
       <c r="K17" s="3">
         <v>400</v>
       </c>
       <c r="L17" s="3">
+        <v>400</v>
+      </c>
+      <c r="M17" s="3">
         <v>1000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>500</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
@@ -1547,8 +1574,8 @@
       <c r="R17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T17" s="3">
         <v>0</v>
@@ -1589,44 +1616,47 @@
       <c r="AF17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E18" s="3">
         <v>3800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3900</v>
-      </c>
-      <c r="F18" s="3">
-        <v>3800</v>
       </c>
       <c r="G18" s="3">
         <v>3800</v>
       </c>
       <c r="H18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I18" s="3">
         <v>7100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2800</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1639,8 +1669,8 @@
       <c r="R18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T18" s="3">
         <v>0</v>
@@ -1681,8 +1711,11 @@
       <c r="AF18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1748,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1727,32 +1761,32 @@
         <v>-2500</v>
       </c>
       <c r="F20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="G20" s="3">
         <v>-2700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-3600</v>
       </c>
       <c r="L20" s="3">
         <v>-3600</v>
       </c>
       <c r="M20" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1800</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
@@ -1765,86 +1799,89 @@
       <c r="R20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="3">
         <v>1200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1100</v>
-      </c>
-      <c r="W20" s="3">
-        <v>1300</v>
       </c>
       <c r="X20" s="3">
         <v>1300</v>
       </c>
       <c r="Y20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Z20" s="3">
         <v>1200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1000</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>1100</v>
       </c>
       <c r="AE20" s="3">
         <v>1100</v>
       </c>
       <c r="AF20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AG20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E21" s="3">
         <v>1400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1100</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1899,8 +1936,11 @@
       <c r="AF21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,100 +2031,106 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E23" s="3">
         <v>1300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1000</v>
-      </c>
-      <c r="R23" s="3">
-        <v>1200</v>
       </c>
       <c r="S23" s="3">
         <v>1200</v>
       </c>
       <c r="T23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="U23" s="3">
         <v>1100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1100</v>
-      </c>
-      <c r="W23" s="3">
-        <v>1300</v>
       </c>
       <c r="X23" s="3">
         <v>1300</v>
       </c>
       <c r="Y23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Z23" s="3">
         <v>1200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1000</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>1100</v>
       </c>
       <c r="AE23" s="3">
         <v>1100</v>
       </c>
       <c r="AF23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AG23" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2095,43 +2141,43 @@
         <v>300</v>
       </c>
       <c r="F24" s="3">
+        <v>300</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
-      </c>
-      <c r="R24" s="3">
-        <v>300</v>
       </c>
       <c r="S24" s="3">
         <v>300</v>
@@ -2140,34 +2186,34 @@
         <v>300</v>
       </c>
       <c r="U24" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V24" s="3">
         <v>200</v>
       </c>
       <c r="W24" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X24" s="3">
         <v>300</v>
       </c>
       <c r="Y24" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>300</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>400</v>
       </c>
       <c r="AE24" s="3">
         <v>400</v>
@@ -2175,8 +2221,11 @@
       <c r="AF24" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,44 +2316,47 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E26" s="3">
         <v>1000</v>
       </c>
       <c r="F26" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="G26" s="3">
         <v>900</v>
       </c>
       <c r="H26" s="3">
+        <v>900</v>
+      </c>
+      <c r="I26" s="3">
         <v>2300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>800</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
@@ -2317,8 +2369,8 @@
       <c r="R26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T26" s="3">
         <v>0</v>
@@ -2359,13 +2411,16 @@
       <c r="AF26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E27" s="3">
         <v>1000</v>
@@ -2374,29 +2429,29 @@
         <v>1000</v>
       </c>
       <c r="G27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H27" s="3">
         <v>900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>800</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
@@ -2409,8 +2464,8 @@
       <c r="R27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T27" s="3">
         <v>0</v>
@@ -2451,8 +2506,11 @@
       <c r="AF27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2886,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2831,32 +2901,32 @@
         <v>2500</v>
       </c>
       <c r="F32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G32" s="3">
         <v>2700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>3600</v>
       </c>
       <c r="L32" s="3">
         <v>3600</v>
       </c>
       <c r="M32" s="3">
+        <v>3600</v>
+      </c>
+      <c r="N32" s="3">
         <v>1800</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
@@ -2869,55 +2939,58 @@
       <c r="R32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3">
         <v>-1200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1100</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-1300</v>
       </c>
       <c r="X32" s="3">
         <v>-1300</v>
       </c>
       <c r="Y32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-1100</v>
       </c>
       <c r="AE32" s="3">
         <v>-1100</v>
       </c>
       <c r="AF32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E33" s="3">
         <v>1000</v>
@@ -2926,29 +2999,29 @@
         <v>1000</v>
       </c>
       <c r="G33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H33" s="3">
         <v>900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>800</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
@@ -2961,8 +3034,8 @@
       <c r="R33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T33" s="3">
         <v>0</v>
@@ -3003,8 +3076,11 @@
       <c r="AF33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,13 +3171,16 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E35" s="3">
         <v>1000</v>
@@ -3110,29 +3189,29 @@
         <v>1000</v>
       </c>
       <c r="G35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H35" s="3">
         <v>900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>800</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
@@ -3145,8 +3224,8 @@
       <c r="R35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T35" s="3">
         <v>0</v>
@@ -3187,105 +3266,111 @@
       <c r="AF35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,44 +3438,45 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E41" s="3">
         <v>3800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3200</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3402,8 +3489,8 @@
       <c r="R41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
+      <c r="S41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T41" s="3">
         <v>0</v>
@@ -3444,44 +3531,47 @@
       <c r="AF41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E42" s="3">
         <v>22400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>25200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>30200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>23700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>21100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>34900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>59700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>86600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>91200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>53900</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3494,8 +3584,8 @@
       <c r="R42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -3536,8 +3626,11 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3628,8 +3721,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,8 +3816,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3812,8 +3911,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3904,8 +4006,11 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,44 +4101,47 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E48" s="3">
         <v>11500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8500</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4046,8 +4154,8 @@
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
@@ -4088,8 +4196,11 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,43 +4481,46 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E52" s="3">
         <v>2400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1400</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1000</v>
       </c>
       <c r="M52" s="3">
         <v>1000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
+      <c r="N52" s="3">
+        <v>1000</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>4</v>
@@ -4414,8 +4534,8 @@
       <c r="R52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>417300</v>
+      </c>
+      <c r="E54" s="3">
         <v>417900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>417500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>423200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>406100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>384000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>353500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>354700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>372600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>376200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>334100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>331400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>326100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>330700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>312500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>298100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>302900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>299500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>299600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>293400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>297200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>301800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>290200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>284200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>282900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>286300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>283900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>274100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>274500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>258800</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4838,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4723,7 +4854,7 @@
         <v>200</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H57" s="3">
         <v>0</v>
@@ -4732,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
@@ -4743,8 +4874,8 @@
       <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
+      <c r="N57" s="3">
+        <v>100</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>4</v>
@@ -4755,8 +4886,8 @@
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
+      <c r="R57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
@@ -4800,8 +4931,11 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4892,8 +5026,11 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4939,11 +5076,11 @@
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S59" s="3">
-        <v>0</v>
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T59" s="3">
         <v>0</v>
@@ -4984,8 +5121,11 @@
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5076,8 +5216,11 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5168,8 +5311,11 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,8 +5691,11 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5545,35 +5703,35 @@
         <v>316100</v>
       </c>
       <c r="E66" s="3">
+        <v>316100</v>
+      </c>
+      <c r="F66" s="3">
         <v>317000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>323000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>307600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>285300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>254900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>255000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>273800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>318400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>277500</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>4</v>
       </c>
@@ -5586,8 +5744,8 @@
       <c r="R66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S66" s="3">
-        <v>0</v>
+      <c r="S66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T66" s="3">
         <v>0</v>
@@ -5628,8 +5786,11 @@
       <c r="AF66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,44 +6201,47 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>58500</v>
+      </c>
+      <c r="E72" s="3">
         <v>57400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>56400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>56600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>55600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>54700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>53400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>53300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>52600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>50500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>49600</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
@@ -6080,8 +6254,8 @@
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
+      <c r="S72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T72" s="3">
         <v>0</v>
@@ -6122,8 +6296,11 @@
       <c r="AF72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>101200</v>
+      </c>
+      <c r="E76" s="3">
         <v>101700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>100600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>100200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>98500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>98700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>98600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>99700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>98800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>57800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>56600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>56900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>55600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>54500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>53000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>53400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>53100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>52200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>51100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>50700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>49400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>48500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>47500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>46900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>45000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>45700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>46000</v>
-      </c>
-      <c r="AD76" s="3">
-        <v>45300</v>
       </c>
       <c r="AE76" s="3">
         <v>45300</v>
       </c>
       <c r="AF76" s="3">
+        <v>45300</v>
+      </c>
+      <c r="AG76" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,110 +6771,116 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E81" s="3">
         <v>1000</v>
@@ -6694,29 +6889,29 @@
         <v>1000</v>
       </c>
       <c r="G81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H81" s="3">
         <v>900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>800</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
@@ -6729,8 +6924,8 @@
       <c r="R81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T81" s="3">
         <v>0</v>
@@ -6771,8 +6966,11 @@
       <c r="AF81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7003,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6817,16 +7016,16 @@
         <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200</v>
-      </c>
-      <c r="I83" s="3">
-        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
@@ -6835,14 +7034,14 @@
         <v>100</v>
       </c>
       <c r="L83" s="3">
+        <v>100</v>
+      </c>
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
@@ -6855,8 +7054,8 @@
       <c r="R83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,44 +7571,47 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1500</v>
+        <v>2400</v>
       </c>
       <c r="E89" s="3">
         <v>1500</v>
       </c>
       <c r="F89" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G89" s="3">
         <v>500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>700</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>4</v>
       </c>
@@ -7407,8 +7624,8 @@
       <c r="R89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
+      <c r="S89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T89" s="3">
         <v>0</v>
@@ -7449,8 +7666,11 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,25 +7703,26 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-900</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-300</v>
       </c>
       <c r="I91" s="3">
         <v>-300</v>
@@ -7510,17 +7731,17 @@
         <v>-300</v>
       </c>
       <c r="K91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
@@ -7533,8 +7754,8 @@
       <c r="R91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -7575,8 +7796,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,44 +7986,47 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-19700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-69100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-23300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5900</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
@@ -7809,8 +8039,8 @@
       <c r="R94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -7851,8 +8081,11 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7894,34 +8128,34 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>-900</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
         <v>-900</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
       <c r="L96" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="M96" s="3">
         <v>-900</v>
       </c>
       <c r="N96" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,44 +8496,47 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>16100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>21500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>28900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-18600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>42600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
@@ -8303,8 +8549,8 @@
       <c r="R100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
+      <c r="S100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
@@ -8345,8 +8591,11 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,44 +8686,47 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-37200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-23300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-27800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>32800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3200</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>4</v>
       </c>
@@ -8487,8 +8739,8 @@
       <c r="R102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
+      <c r="S102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T102" s="3">
         <v>0</v>
@@ -8527,6 +8779,9 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CULL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CULL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
   <si>
     <t>CULL</t>
   </si>
@@ -656,144 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -801,40 +808,40 @@
         <v>5100</v>
       </c>
       <c r="E8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F8" s="3">
+        <v>5100</v>
+      </c>
+      <c r="G8" s="3">
         <v>4800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>4700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>4600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>4200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>7700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3400</v>
-      </c>
-      <c r="L8" s="3">
-        <v>3300</v>
-      </c>
-      <c r="M8" s="3">
-        <v>6700</v>
       </c>
       <c r="N8" s="3">
         <v>3300</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
+      <c r="O8" s="3">
+        <v>6700</v>
+      </c>
+      <c r="P8" s="3">
+        <v>3300</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>4</v>
@@ -845,11 +852,11 @@
       <c r="S8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="T8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
@@ -887,8 +894,14 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -982,8 +995,14 @@
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1096,14 @@
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1137,10 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1207,8 +1234,14 @@
       <c r="AG12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1335,14 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1397,8 +1436,14 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1537,14 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,50 +1575,52 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F17" s="3">
         <v>1200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>500</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
@@ -1577,11 +1630,11 @@
       <c r="S17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
-      <c r="U17" s="3">
-        <v>0</v>
+      <c r="T17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V17" s="3">
         <v>0</v>
@@ -1619,16 +1672,22 @@
       <c r="AG17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3900</v>
+        <v>3600</v>
       </c>
       <c r="E18" s="3">
-        <v>3800</v>
+        <v>3400</v>
       </c>
       <c r="F18" s="3">
         <v>3900</v>
@@ -1637,32 +1696,32 @@
         <v>3800</v>
       </c>
       <c r="H18" s="3">
+        <v>3900</v>
+      </c>
+      <c r="I18" s="3">
         <v>3800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K18" s="3">
         <v>7100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>3300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>3000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>5700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>2800</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1672,11 +1731,11 @@
       <c r="S18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
-      <c r="U18" s="3">
-        <v>0</v>
+      <c r="T18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V18" s="3">
         <v>0</v>
@@ -1714,8 +1773,14 @@
       <c r="AG18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,13 +1814,15 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2500</v>
+        <v>-2700</v>
       </c>
       <c r="E20" s="3">
         <v>-2500</v>
@@ -1764,35 +1831,35 @@
         <v>-2500</v>
       </c>
       <c r="G20" s="3">
-        <v>-2700</v>
+        <v>-2500</v>
       </c>
       <c r="H20" s="3">
         <v>-2500</v>
       </c>
       <c r="I20" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-4200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-2300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-3600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-3600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-1800</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
@@ -1802,11 +1869,11 @@
       <c r="S20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="U20" s="3">
-        <v>1100</v>
+      <c r="T20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V20" s="3">
         <v>1200</v>
@@ -1815,79 +1882,85 @@
         <v>1100</v>
       </c>
       <c r="X20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z20" s="3">
         <v>1300</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>1200</v>
       </c>
       <c r="AA20" s="3">
         <v>1300</v>
       </c>
       <c r="AB20" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="AC20" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="AD20" s="3">
         <v>1000</v>
       </c>
       <c r="AE20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG20" s="3">
         <v>1100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>1100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="E21" s="3">
-        <v>1400</v>
+        <v>1100</v>
       </c>
       <c r="F21" s="3">
         <v>1500</v>
       </c>
       <c r="G21" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I21" s="3">
         <v>1100</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I21" s="3">
-        <v>3200</v>
       </c>
       <c r="J21" s="3">
         <v>1400</v>
       </c>
       <c r="K21" s="3">
+        <v>3200</v>
+      </c>
+      <c r="L21" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M21" s="3">
         <v>800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1100</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1939,8 +2012,14 @@
       <c r="AG21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2034,64 +2113,70 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1400</v>
+        <v>900</v>
       </c>
       <c r="E23" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="F23" s="3">
         <v>1400</v>
       </c>
       <c r="G23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I23" s="3">
         <v>1100</v>
-      </c>
-      <c r="H23" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I23" s="3">
-        <v>2900</v>
       </c>
       <c r="J23" s="3">
         <v>1300</v>
       </c>
       <c r="K23" s="3">
+        <v>2900</v>
+      </c>
+      <c r="L23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M23" s="3">
         <v>700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>2100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>900</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>1200</v>
-      </c>
-      <c r="R23" s="3">
-        <v>1000</v>
       </c>
       <c r="S23" s="3">
         <v>1200</v>
       </c>
       <c r="T23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U23" s="3">
         <v>1200</v>
-      </c>
-      <c r="U23" s="3">
-        <v>1100</v>
       </c>
       <c r="V23" s="3">
         <v>1200</v>
@@ -2100,75 +2185,81 @@
         <v>1100</v>
       </c>
       <c r="X23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z23" s="3">
         <v>1300</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>1200</v>
       </c>
       <c r="AA23" s="3">
         <v>1300</v>
       </c>
       <c r="AB23" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="AC23" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="AD23" s="3">
         <v>1000</v>
       </c>
       <c r="AE23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG23" s="3">
         <v>1100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>1100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F24" s="3">
         <v>300</v>
       </c>
       <c r="G24" s="3">
+        <v>300</v>
+      </c>
+      <c r="H24" s="3">
+        <v>300</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
-      </c>
-      <c r="N24" s="3">
-        <v>200</v>
-      </c>
-      <c r="O24" s="3">
-        <v>300</v>
       </c>
       <c r="P24" s="3">
         <v>200</v>
@@ -2183,34 +2274,34 @@
         <v>300</v>
       </c>
       <c r="T24" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U24" s="3">
         <v>300</v>
       </c>
       <c r="V24" s="3">
+        <v>300</v>
+      </c>
+      <c r="W24" s="3">
+        <v>300</v>
+      </c>
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>800</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>300</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>400</v>
       </c>
       <c r="AD24" s="3">
         <v>300</v>
@@ -2219,13 +2310,19 @@
         <v>400</v>
       </c>
       <c r="AF24" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AG24" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,50 +2416,56 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>800</v>
+      </c>
+      <c r="F26" s="3">
         <v>1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>800</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
@@ -2372,11 +2475,11 @@
       <c r="S26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
-      <c r="U26" s="3">
-        <v>0</v>
+      <c r="T26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V26" s="3">
         <v>0</v>
@@ -2414,50 +2517,56 @@
       <c r="AG26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>800</v>
+      </c>
+      <c r="F27" s="3">
         <v>1100</v>
-      </c>
-      <c r="E27" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F27" s="3">
-        <v>1000</v>
       </c>
       <c r="G27" s="3">
         <v>1000</v>
       </c>
       <c r="H27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I27" s="3">
         <v>900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
+        <v>900</v>
+      </c>
+      <c r="K27" s="3">
         <v>2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>800</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
@@ -2467,11 +2576,11 @@
       <c r="S27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
-      <c r="U27" s="3">
-        <v>0</v>
+      <c r="T27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V27" s="3">
         <v>0</v>
@@ -2509,8 +2618,14 @@
       <c r="AG27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2719,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2820,14 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2921,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,13 +3022,19 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="E32" s="3">
         <v>2500</v>
@@ -2904,35 +3043,35 @@
         <v>2500</v>
       </c>
       <c r="G32" s="3">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="H32" s="3">
         <v>2500</v>
       </c>
       <c r="I32" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K32" s="3">
         <v>4200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>2300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>3600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>3600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>1800</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
@@ -2942,11 +3081,11 @@
       <c r="S32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-1100</v>
+      <c r="T32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V32" s="3">
         <v>-1200</v>
@@ -2955,79 +3094,85 @@
         <v>-1100</v>
       </c>
       <c r="X32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-1300</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-1200</v>
       </c>
       <c r="AA32" s="3">
         <v>-1300</v>
       </c>
       <c r="AB32" s="3">
-        <v>-1000</v>
+        <v>-1200</v>
       </c>
       <c r="AC32" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="AD32" s="3">
         <v>-1000</v>
       </c>
       <c r="AE32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>800</v>
+      </c>
+      <c r="F33" s="3">
         <v>1100</v>
-      </c>
-      <c r="E33" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1000</v>
       </c>
       <c r="G33" s="3">
         <v>1000</v>
       </c>
       <c r="H33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I33" s="3">
         <v>900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
+        <v>900</v>
+      </c>
+      <c r="K33" s="3">
         <v>2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>800</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
@@ -3037,11 +3182,11 @@
       <c r="S33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
-      <c r="U33" s="3">
-        <v>0</v>
+      <c r="T33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V33" s="3">
         <v>0</v>
@@ -3079,8 +3224,14 @@
       <c r="AG33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,50 +3325,56 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>800</v>
+      </c>
+      <c r="F35" s="3">
         <v>1100</v>
-      </c>
-      <c r="E35" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F35" s="3">
-        <v>1000</v>
       </c>
       <c r="G35" s="3">
         <v>1000</v>
       </c>
       <c r="H35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I35" s="3">
         <v>900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
+        <v>900</v>
+      </c>
+      <c r="K35" s="3">
         <v>2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>800</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
@@ -3227,11 +3384,11 @@
       <c r="S35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3">
-        <v>0</v>
+      <c r="T35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V35" s="3">
         <v>0</v>
@@ -3269,108 +3426,120 @@
       <c r="AG35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3573,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,50 +3610,52 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F41" s="3">
         <v>3700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>6400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>5000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>3200</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3492,11 +3665,11 @@
       <c r="S41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
-      <c r="U41" s="3">
-        <v>0</v>
+      <c r="T41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V41" s="3">
         <v>0</v>
@@ -3534,50 +3707,56 @@
       <c r="AG41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F42" s="3">
         <v>19100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>22400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>25200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>30200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>23700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>21100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>34900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>59700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>86600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>91200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>53900</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3587,11 +3766,11 @@
       <c r="S42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -3629,8 +3808,14 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3724,8 +3909,14 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3819,8 +4010,14 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3914,8 +4111,14 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4009,8 +4212,14 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4104,50 +4313,56 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F48" s="3">
         <v>12000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>11500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>10800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>10900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>10100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>9800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>9600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>9500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>9300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>8700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>8500</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4157,11 +4372,11 @@
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
-      </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -4199,8 +4414,14 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4294,8 +4515,14 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4616,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,22 +4717,28 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="E52" s="3">
         <v>2400</v>
       </c>
       <c r="F52" s="3">
-        <v>2300</v>
+        <v>2700</v>
       </c>
       <c r="G52" s="3">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="H52" s="3">
         <v>2300</v>
@@ -4508,26 +4747,26 @@
         <v>2200</v>
       </c>
       <c r="J52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K52" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L52" s="3">
         <v>1700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4537,11 +4776,11 @@
       <c r="S52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
-      </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -4579,8 +4818,14 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4919,115 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>420700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>411600</v>
+      </c>
+      <c r="F54" s="3">
         <v>417300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>417900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>417500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>423200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>406100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>384000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>353500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>354700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>372600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>376200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>334100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>331400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>326100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>330700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>312500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>298100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>302900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>299500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>299600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>293400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>297200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>301800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>290200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>284200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>282900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>286300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>283900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>274100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>274500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>258800</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +5061,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,13 +5098,15 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E57" s="3">
         <v>200</v>
@@ -4857,19 +5118,19 @@
         <v>200</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J57" s="3">
         <v>0</v>
       </c>
       <c r="K57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M57" s="3">
         <v>100</v>
@@ -4877,11 +5138,11 @@
       <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
+      <c r="O57" s="3">
+        <v>100</v>
+      </c>
+      <c r="P57" s="3">
+        <v>100</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>4</v>
@@ -4889,11 +5150,11 @@
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
-      <c r="T57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
@@ -4934,8 +5195,14 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5029,8 +5296,14 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5079,14 +5352,14 @@
       <c r="R59" s="3">
         <v>0</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>4</v>
+      <c r="S59" s="3">
+        <v>0</v>
       </c>
       <c r="T59" s="3">
         <v>0</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
+      <c r="U59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V59" s="3">
         <v>0</v>
@@ -5124,8 +5397,14 @@
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5219,8 +5498,14 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5314,8 +5599,14 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5409,8 +5700,14 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5801,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5902,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,50 +6003,56 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>319400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>309900</v>
+      </c>
+      <c r="F66" s="3">
         <v>316100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>316100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>317000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>323000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>307600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>285300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>254900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>255000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>273800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>318400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>277500</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>4</v>
       </c>
@@ -5747,11 +6062,11 @@
       <c r="S66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T66" s="3">
-        <v>0</v>
-      </c>
-      <c r="U66" s="3">
-        <v>0</v>
+      <c r="T66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V66" s="3">
         <v>0</v>
@@ -5789,8 +6104,14 @@
       <c r="AG66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +6145,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6242,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6343,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6444,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,50 +6545,56 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>59200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>59300</v>
+      </c>
+      <c r="F72" s="3">
         <v>58500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>57400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>56400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>56600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>55600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>54700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>53400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>53300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>52600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>50500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>49600</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
@@ -6257,11 +6604,11 @@
       <c r="S72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
-      <c r="U72" s="3">
-        <v>0</v>
+      <c r="T72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V72" s="3">
         <v>0</v>
@@ -6299,8 +6646,14 @@
       <c r="AG72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6747,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6848,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6949,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>101200</v>
+        <v>101300</v>
       </c>
       <c r="E76" s="3">
         <v>101700</v>
       </c>
       <c r="F76" s="3">
+        <v>101200</v>
+      </c>
+      <c r="G76" s="3">
+        <v>101700</v>
+      </c>
+      <c r="H76" s="3">
         <v>100600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>100200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>98500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>98700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>98600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>99700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>98800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>57800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>56600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>56900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>55600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>54500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>53000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>53400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>53100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>52200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>51100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>50700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>49400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>48500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>47500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>46900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>45000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>45700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>46000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>45300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>45300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,150 +7151,162 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>800</v>
+      </c>
+      <c r="F81" s="3">
         <v>1100</v>
-      </c>
-      <c r="E81" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F81" s="3">
-        <v>1000</v>
       </c>
       <c r="G81" s="3">
         <v>1000</v>
       </c>
       <c r="H81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I81" s="3">
         <v>900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
+        <v>900</v>
+      </c>
+      <c r="K81" s="3">
         <v>2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>800</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
@@ -6927,11 +7316,11 @@
       <c r="S81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
-      <c r="U81" s="3">
-        <v>0</v>
+      <c r="T81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V81" s="3">
         <v>0</v>
@@ -6969,8 +7358,14 @@
       <c r="AG81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7399,10 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7019,34 +7416,34 @@
         <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L83" s="3">
         <v>100</v>
       </c>
       <c r="M83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
+      <c r="O83" s="3">
+        <v>200</v>
+      </c>
+      <c r="P83" s="3">
+        <v>100</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>4</v>
@@ -7057,11 +7454,11 @@
       <c r="S83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -7099,8 +7496,14 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7597,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7698,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7799,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7900,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,50 +8001,56 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>500</v>
+      </c>
+      <c r="F89" s="3">
         <v>2400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>3100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>2900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>700</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>4</v>
       </c>
@@ -7627,11 +8060,11 @@
       <c r="S89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3">
-        <v>0</v>
+      <c r="T89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V89" s="3">
         <v>0</v>
@@ -7669,8 +8102,14 @@
       <c r="AG89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,50 +8143,52 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-300</v>
       </c>
       <c r="K91" s="3">
         <v>-300</v>
       </c>
       <c r="L91" s="3">
-        <v>-600</v>
+        <v>-300</v>
       </c>
       <c r="M91" s="3">
         <v>-300</v>
       </c>
       <c r="N91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
@@ -7757,11 +8198,11 @@
       <c r="S91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -7799,8 +8240,14 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8341,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,50 +8442,56 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-3800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-2900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-8700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-19700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-69100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-23300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-10100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-11200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-5900</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
@@ -8042,11 +8501,11 @@
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -8084,8 +8543,14 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,50 +8584,52 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>-900</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-900</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-900</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -8214,8 +8681,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8782,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8883,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,50 +8984,56 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-7500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>16100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>21500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>28900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-18600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-4900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>42600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>2100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>4</v>
       </c>
@@ -8552,11 +9043,11 @@
       <c r="S100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
+      <c r="T100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
@@ -8594,8 +9085,14 @@
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8689,50 +9186,56 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-8900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>7900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>4000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-37200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-23300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-27800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>32800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3200</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>4</v>
       </c>
@@ -8742,11 +9245,11 @@
       <c r="S102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
-      <c r="U102" s="3">
-        <v>0</v>
+      <c r="T102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V102" s="3">
         <v>0</v>
@@ -8782,6 +9285,12 @@
         <v>0</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CULL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CULL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
   <si>
     <t>CULL</t>
   </si>
@@ -805,22 +805,22 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5100</v>
+        <v>4000</v>
       </c>
       <c r="E8" s="3">
-        <v>5000</v>
+        <v>3900</v>
       </c>
       <c r="F8" s="3">
-        <v>5100</v>
+        <v>4300</v>
       </c>
       <c r="G8" s="3">
-        <v>4800</v>
+        <v>4200</v>
       </c>
       <c r="H8" s="3">
-        <v>4700</v>
+        <v>4200</v>
       </c>
       <c r="I8" s="3">
-        <v>4600</v>
+        <v>4300</v>
       </c>
       <c r="J8" s="3">
         <v>4200</v>
@@ -1006,26 +1006,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F10" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G10" s="3">
+        <v>4200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I10" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>4200</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
@@ -1346,26 +1346,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1448,25 +1448,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1583,25 +1583,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="E17" s="3">
-        <v>1600</v>
+        <v>2800</v>
       </c>
       <c r="F17" s="3">
-        <v>1200</v>
+        <v>2800</v>
       </c>
       <c r="G17" s="3">
-        <v>1000</v>
+        <v>2900</v>
       </c>
       <c r="H17" s="3">
-        <v>800</v>
+        <v>2800</v>
       </c>
       <c r="I17" s="3">
-        <v>800</v>
+        <v>3200</v>
       </c>
       <c r="J17" s="3">
-        <v>400</v>
+        <v>2900</v>
       </c>
       <c r="K17" s="3">
         <v>600</v>
@@ -1684,25 +1684,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3600</v>
+        <v>900</v>
       </c>
       <c r="E18" s="3">
-        <v>3400</v>
+        <v>1000</v>
       </c>
       <c r="F18" s="3">
-        <v>3900</v>
+        <v>1400</v>
       </c>
       <c r="G18" s="3">
-        <v>3800</v>
+        <v>1200</v>
       </c>
       <c r="H18" s="3">
-        <v>3900</v>
+        <v>1400</v>
       </c>
       <c r="I18" s="3">
-        <v>3800</v>
+        <v>1100</v>
       </c>
       <c r="J18" s="3">
-        <v>3800</v>
+        <v>1300</v>
       </c>
       <c r="K18" s="3">
         <v>7100</v>
@@ -1822,25 +1822,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2700</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>-2500</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>-2500</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-2500</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>-2500</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>-2700</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>-2500</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>-4200</v>
@@ -1932,7 +1932,7 @@
         <v>1500</v>
       </c>
       <c r="G21" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="H21" s="3">
         <v>1500</v>
@@ -2023,26 +2023,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -3034,25 +3034,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>2500</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>4200</v>
@@ -3618,25 +3618,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3800</v>
+        <v>17400</v>
       </c>
       <c r="E41" s="3">
-        <v>4400</v>
+        <v>13000</v>
       </c>
       <c r="F41" s="3">
-        <v>3700</v>
+        <v>22800</v>
       </c>
       <c r="G41" s="3">
-        <v>3800</v>
+        <v>26200</v>
       </c>
       <c r="H41" s="3">
-        <v>2500</v>
+        <v>27700</v>
       </c>
       <c r="I41" s="3">
-        <v>6400</v>
+        <v>36600</v>
       </c>
       <c r="J41" s="3">
-        <v>5000</v>
+        <v>28700</v>
       </c>
       <c r="K41" s="3">
         <v>3700</v>
@@ -3719,25 +3719,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>13500</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>19100</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>22400</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>25200</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>30200</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>23700</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>21100</v>
@@ -3819,26 +3819,26 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3920,26 +3920,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4022,25 +4022,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4123,25 +4123,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>18700</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>14300</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>23900</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>27400</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>28900</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>37900</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>29900</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4224,25 +4224,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>27700</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>28400</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>27300</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>29400</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>29800</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>30300</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>28600</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4729,25 +4729,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2500</v>
+        <v>13100</v>
       </c>
       <c r="E52" s="3">
-        <v>2400</v>
+        <v>13100</v>
       </c>
       <c r="F52" s="3">
-        <v>2700</v>
+        <v>13300</v>
       </c>
       <c r="G52" s="3">
-        <v>2400</v>
+        <v>12900</v>
       </c>
       <c r="H52" s="3">
-        <v>2300</v>
+        <v>12900</v>
       </c>
       <c r="I52" s="3">
-        <v>2200</v>
+        <v>12100</v>
       </c>
       <c r="J52" s="3">
-        <v>2300</v>
+        <v>9600</v>
       </c>
       <c r="K52" s="3">
         <v>2200</v>
@@ -5106,25 +5106,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>400</v>
+        <v>268400</v>
       </c>
       <c r="E57" s="3">
-        <v>200</v>
+        <v>269000</v>
       </c>
       <c r="F57" s="3">
-        <v>200</v>
+        <v>274200</v>
       </c>
       <c r="G57" s="3">
-        <v>200</v>
+        <v>275200</v>
       </c>
       <c r="H57" s="3">
-        <v>200</v>
+        <v>276500</v>
       </c>
       <c r="I57" s="3">
-        <v>200</v>
+        <v>292900</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>286800</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5307,26 +5307,26 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -5409,25 +5409,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>268800</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>269200</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>274400</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>275400</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>276600</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>293100</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>286800</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5510,25 +5510,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>35100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5611,25 +5611,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>6700</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -7410,7 +7410,7 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -7422,7 +7422,7 @@
         <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
@@ -8592,7 +8592,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-900</v>
+        <v>900</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -8604,7 +8604,7 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-900</v>
+        <v>900</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -9096,26 +9096,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/CULL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CULL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
   <si>
     <t>CULL</t>
   </si>
@@ -656,196 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E8" s="3">
         <v>4000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4300</v>
-      </c>
-      <c r="G8" s="3">
-        <v>4200</v>
       </c>
       <c r="H8" s="3">
         <v>4200</v>
       </c>
       <c r="I8" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J8" s="3">
         <v>4300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3300</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>4</v>
       </c>
@@ -858,8 +861,8 @@
       <c r="U8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="V8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
@@ -900,8 +903,11 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1001,35 +1007,38 @@
       <c r="AI9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E10" s="3">
         <v>4000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4300</v>
-      </c>
-      <c r="G10" s="3">
-        <v>4200</v>
       </c>
       <c r="H10" s="3">
         <v>4200</v>
       </c>
       <c r="I10" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J10" s="3">
         <v>4300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4200</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1102,8 +1111,11 @@
       <c r="AI10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1151,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1240,8 +1253,11 @@
       <c r="AI12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,34 +1357,37 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>-100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1442,8 +1461,11 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1463,14 +1485,14 @@
         <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1543,8 +1565,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,53 +1602,54 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E17" s="3">
         <v>3000</v>
-      </c>
-      <c r="E17" s="3">
-        <v>2800</v>
       </c>
       <c r="F17" s="3">
         <v>2800</v>
       </c>
       <c r="G17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H17" s="3">
         <v>2900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>300</v>
-      </c>
-      <c r="M17" s="3">
-        <v>400</v>
       </c>
       <c r="N17" s="3">
         <v>400</v>
       </c>
       <c r="O17" s="3">
+        <v>400</v>
+      </c>
+      <c r="P17" s="3">
         <v>1000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>4</v>
       </c>
@@ -1636,8 +1662,8 @@
       <c r="U17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
+      <c r="V17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W17" s="3">
         <v>0</v>
@@ -1678,53 +1704,56 @@
       <c r="AI17" s="3">
         <v>0</v>
       </c>
+      <c r="AJ17" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E18" s="3">
         <v>900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2800</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1737,8 +1766,8 @@
       <c r="U18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
+      <c r="V18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W18" s="3">
         <v>0</v>
@@ -1779,8 +1808,11 @@
       <c r="AI18" s="3">
         <v>0</v>
       </c>
+      <c r="AJ18" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,8 +1848,9 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1831,11 +1864,11 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1843,26 +1876,26 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-4200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-3600</v>
       </c>
       <c r="O20" s="3">
         <v>-3600</v>
       </c>
       <c r="P20" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>4</v>
       </c>
@@ -1875,95 +1908,98 @@
       <c r="U20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W20" s="3">
         <v>1200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1100</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>1300</v>
       </c>
       <c r="AA20" s="3">
         <v>1300</v>
       </c>
       <c r="AB20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AC20" s="3">
         <v>1200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1000</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>1100</v>
       </c>
       <c r="AH20" s="3">
         <v>1100</v>
       </c>
       <c r="AI20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1100</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2018,8 +2054,11 @@
       <c r="AI21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2044,8 +2083,8 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2119,109 +2158,115 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E23" s="3">
         <v>900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1000</v>
-      </c>
-      <c r="U23" s="3">
-        <v>1200</v>
       </c>
       <c r="V23" s="3">
         <v>1200</v>
       </c>
       <c r="W23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X23" s="3">
         <v>1100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1100</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>1300</v>
       </c>
       <c r="AA23" s="3">
         <v>1300</v>
       </c>
       <c r="AB23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AC23" s="3">
         <v>1200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1000</v>
-      </c>
-      <c r="AG23" s="3">
-        <v>1100</v>
       </c>
       <c r="AH23" s="3">
         <v>1100</v>
       </c>
       <c r="AI23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2232,7 +2277,7 @@
         <v>200</v>
       </c>
       <c r="F24" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G24" s="3">
         <v>300</v>
@@ -2241,43 +2286,43 @@
         <v>300</v>
       </c>
       <c r="I24" s="3">
+        <v>300</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
-      </c>
-      <c r="U24" s="3">
-        <v>300</v>
       </c>
       <c r="V24" s="3">
         <v>300</v>
@@ -2286,34 +2331,34 @@
         <v>300</v>
       </c>
       <c r="X24" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y24" s="3">
         <v>200</v>
       </c>
       <c r="Z24" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AA24" s="3">
         <v>300</v>
       </c>
       <c r="AB24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>300</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>400</v>
       </c>
       <c r="AH24" s="3">
         <v>400</v>
@@ -2321,8 +2366,11 @@
       <c r="AI24" s="3">
         <v>400</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,53 +2470,56 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>900</v>
+      </c>
+      <c r="E26" s="3">
         <v>700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1100</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1000</v>
       </c>
       <c r="H26" s="3">
         <v>1000</v>
       </c>
       <c r="I26" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J26" s="3">
         <v>900</v>
       </c>
       <c r="K26" s="3">
+        <v>900</v>
+      </c>
+      <c r="L26" s="3">
         <v>2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>800</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>4</v>
       </c>
@@ -2481,8 +2532,8 @@
       <c r="U26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
+      <c r="V26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W26" s="3">
         <v>0</v>
@@ -2523,53 +2574,56 @@
       <c r="AI26" s="3">
         <v>0</v>
       </c>
+      <c r="AJ26" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>900</v>
+      </c>
+      <c r="E27" s="3">
         <v>700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1100</v>
-      </c>
-      <c r="G27" s="3">
-        <v>1000</v>
       </c>
       <c r="H27" s="3">
         <v>1000</v>
       </c>
       <c r="I27" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J27" s="3">
         <v>900</v>
       </c>
       <c r="K27" s="3">
+        <v>900</v>
+      </c>
+      <c r="L27" s="3">
         <v>2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>800</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>4</v>
       </c>
@@ -2582,8 +2636,8 @@
       <c r="U27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
+      <c r="V27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W27" s="3">
         <v>0</v>
@@ -2624,8 +2678,11 @@
       <c r="AI27" s="3">
         <v>0</v>
       </c>
+      <c r="AJ27" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2782,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2886,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2990,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,8 +3094,11 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3043,11 +3112,11 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -3055,26 +3124,26 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>4200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2300</v>
-      </c>
-      <c r="N32" s="3">
-        <v>3600</v>
       </c>
       <c r="O32" s="3">
         <v>3600</v>
       </c>
       <c r="P32" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Q32" s="3">
         <v>1800</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>4</v>
       </c>
@@ -3087,95 +3156,98 @@
       <c r="U32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W32" s="3">
         <v>-1200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1100</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-1300</v>
       </c>
       <c r="AA32" s="3">
         <v>-1300</v>
       </c>
       <c r="AB32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-1100</v>
       </c>
       <c r="AH32" s="3">
         <v>-1100</v>
       </c>
       <c r="AI32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>900</v>
+      </c>
+      <c r="E33" s="3">
         <v>700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1100</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1000</v>
       </c>
       <c r="H33" s="3">
         <v>1000</v>
       </c>
       <c r="I33" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J33" s="3">
         <v>900</v>
       </c>
       <c r="K33" s="3">
+        <v>900</v>
+      </c>
+      <c r="L33" s="3">
         <v>2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>800</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>4</v>
       </c>
@@ -3188,8 +3260,8 @@
       <c r="U33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
+      <c r="V33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W33" s="3">
         <v>0</v>
@@ -3230,8 +3302,11 @@
       <c r="AI33" s="3">
         <v>0</v>
       </c>
+      <c r="AJ33" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,53 +3406,56 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>900</v>
+      </c>
+      <c r="E35" s="3">
         <v>700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1100</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1000</v>
       </c>
       <c r="H35" s="3">
         <v>1000</v>
       </c>
       <c r="I35" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J35" s="3">
         <v>900</v>
       </c>
       <c r="K35" s="3">
+        <v>900</v>
+      </c>
+      <c r="L35" s="3">
         <v>2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>800</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>4</v>
       </c>
@@ -3390,8 +3468,8 @@
       <c r="U35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
+      <c r="V35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W35" s="3">
         <v>0</v>
@@ -3432,114 +3510,120 @@
       <c r="AI35" s="3">
         <v>0</v>
       </c>
+      <c r="AJ35" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3659,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,53 +3697,54 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E41" s="3">
         <v>17400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>26200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>27700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>36600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>28700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3671,8 +3757,8 @@
       <c r="U41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
+      <c r="V41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W41" s="3">
         <v>0</v>
@@ -3713,8 +3799,11 @@
       <c r="AI41" s="3">
         <v>0</v>
       </c>
+      <c r="AJ41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3740,26 +3829,26 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>21100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>34900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>59700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>86600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>91200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>53900</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3772,8 +3861,8 @@
       <c r="U42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -3814,8 +3903,11 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3840,8 +3932,8 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3915,8 +4007,11 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3932,8 +4027,8 @@
       <c r="G44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H44" s="3">
-        <v>100</v>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I44" s="3">
         <v>100</v>
@@ -3942,7 +4037,7 @@
         <v>100</v>
       </c>
       <c r="K44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4016,35 +4111,38 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="E45" s="3">
         <v>1300</v>
       </c>
       <c r="F45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G45" s="3">
         <v>1100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1100</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -4117,35 +4215,38 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E46" s="3">
         <v>18700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>27400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>28900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>37900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>29900</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4218,35 +4319,38 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E47" s="3">
         <v>27700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>28400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>27300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>29400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>29800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>30300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28600</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -4319,53 +4423,56 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E48" s="3">
         <v>15400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8500</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4378,8 +4485,8 @@
       <c r="U48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -4420,8 +4527,11 @@
       <c r="AI48" s="3">
         <v>0</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4521,8 +4631,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4735,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,52 +4839,55 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>13100</v>
+        <v>13700</v>
       </c>
       <c r="E52" s="3">
         <v>13100</v>
       </c>
       <c r="F52" s="3">
+        <v>13100</v>
+      </c>
+      <c r="G52" s="3">
         <v>13300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>12900</v>
       </c>
       <c r="H52" s="3">
         <v>12900</v>
       </c>
       <c r="I52" s="3">
+        <v>12900</v>
+      </c>
+      <c r="J52" s="3">
         <v>12100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1400</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1000</v>
       </c>
       <c r="P52" s="3">
         <v>1000</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
+      <c r="Q52" s="3">
+        <v>1000</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>4</v>
@@ -4782,8 +4901,8 @@
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -4824,8 +4943,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5047,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>432200</v>
+      </c>
+      <c r="E54" s="3">
         <v>420700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>411600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>417300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>417900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>417500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>423200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>406100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>384000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>353500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>354700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>372600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>376200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>334100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>331400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>326100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>330700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>312500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>298100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>302900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>299500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>299600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>293400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>297200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>301800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>290200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>284200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>282900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>286300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>283900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>274100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>274500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>258800</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5191,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,40 +5229,41 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>280800</v>
+      </c>
+      <c r="E57" s="3">
         <v>268400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>269000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>274200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>275200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>276500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>292900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>286800</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
       <c r="M57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N57" s="3">
         <v>100</v>
@@ -5144,8 +5274,8 @@
       <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>4</v>
+      <c r="Q57" s="3">
+        <v>100</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>4</v>
@@ -5156,8 +5286,8 @@
       <c r="T57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
+      <c r="U57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
@@ -5201,8 +5331,11 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5302,8 +5435,11 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5328,8 +5464,8 @@
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -5358,11 +5494,11 @@
       <c r="T59" s="3">
         <v>0</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V59" s="3">
-        <v>0</v>
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
@@ -5403,35 +5539,38 @@
       <c r="AI59" s="3">
         <v>0</v>
       </c>
+      <c r="AJ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>281100</v>
+      </c>
+      <c r="E60" s="3">
         <v>268800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>269200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>274400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>275400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>276600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>293100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>286800</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5504,8 +5643,11 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5513,10 +5655,10 @@
         <v>45000</v>
       </c>
       <c r="E61" s="3">
+        <v>45000</v>
+      </c>
+      <c r="F61" s="3">
         <v>35100</v>
-      </c>
-      <c r="F61" s="3">
-        <v>35000</v>
       </c>
       <c r="G61" s="3">
         <v>35000</v>
@@ -5525,14 +5667,14 @@
         <v>35000</v>
       </c>
       <c r="I61" s="3">
+        <v>35000</v>
+      </c>
+      <c r="J61" s="3">
         <v>25000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5605,35 +5747,38 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5600</v>
+        <v>6400</v>
       </c>
       <c r="E62" s="3">
         <v>5600</v>
       </c>
       <c r="F62" s="3">
+        <v>5600</v>
+      </c>
+      <c r="G62" s="3">
         <v>6700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5800</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5706,8 +5851,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5955,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6059,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,53 +6163,56 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>332500</v>
+      </c>
+      <c r="E66" s="3">
         <v>319400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>309900</v>
-      </c>
-      <c r="F66" s="3">
-        <v>316100</v>
       </c>
       <c r="G66" s="3">
         <v>316100</v>
       </c>
       <c r="H66" s="3">
+        <v>316100</v>
+      </c>
+      <c r="I66" s="3">
         <v>317000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>323000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>307600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>285300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>254900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>255000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>273800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>318400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>277500</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>4</v>
       </c>
@@ -6068,8 +6225,8 @@
       <c r="U66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V66" s="3">
-        <v>0</v>
+      <c r="V66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W66" s="3">
         <v>0</v>
@@ -6110,8 +6267,11 @@
       <c r="AI66" s="3">
         <v>0</v>
       </c>
+      <c r="AJ66" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6307,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6409,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6513,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6617,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,53 +6721,56 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E72" s="3">
         <v>59200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>59300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>58500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>57400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>56400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>56600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>55600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>54700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>53400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>53300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>52600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>50500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>49600</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
@@ -6610,8 +6783,8 @@
       <c r="U72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
+      <c r="V72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W72" s="3">
         <v>0</v>
@@ -6652,8 +6825,11 @@
       <c r="AI72" s="3">
         <v>0</v>
       </c>
+      <c r="AJ72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6929,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7033,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7137,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>99600</v>
+      </c>
+      <c r="E76" s="3">
         <v>101300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>101700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>101200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>101700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>100600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>100200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>98500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>98700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>98600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>99700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>98800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>57800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>56600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>56900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>55600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>54500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>53000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>53400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>53100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>52200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>51100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>50700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>49400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>48500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>47500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>46900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>45000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>45700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>46000</v>
-      </c>
-      <c r="AG76" s="3">
-        <v>45300</v>
       </c>
       <c r="AH76" s="3">
         <v>45300</v>
       </c>
       <c r="AI76" s="3">
+        <v>45300</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,159 +7345,165 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>900</v>
+      </c>
+      <c r="E81" s="3">
         <v>700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1100</v>
-      </c>
-      <c r="G81" s="3">
-        <v>1000</v>
       </c>
       <c r="H81" s="3">
         <v>1000</v>
       </c>
       <c r="I81" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J81" s="3">
         <v>900</v>
       </c>
       <c r="K81" s="3">
+        <v>900</v>
+      </c>
+      <c r="L81" s="3">
         <v>2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>800</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>4</v>
       </c>
@@ -7322,8 +7516,8 @@
       <c r="U81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
+      <c r="V81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W81" s="3">
         <v>0</v>
@@ -7364,8 +7558,11 @@
       <c r="AI81" s="3">
         <v>0</v>
       </c>
+      <c r="AJ81" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7598,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7410,10 +7608,10 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -7428,10 +7626,10 @@
         <v>100</v>
       </c>
       <c r="K83" s="3">
+        <v>100</v>
+      </c>
+      <c r="L83" s="3">
         <v>200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
@@ -7440,14 +7638,14 @@
         <v>100</v>
       </c>
       <c r="O83" s="3">
+        <v>100</v>
+      </c>
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>100</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>4</v>
       </c>
@@ -7460,8 +7658,8 @@
       <c r="U83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -7502,8 +7700,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7804,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7908,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8012,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8116,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,53 +8220,56 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="3">
         <v>1700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2400</v>
-      </c>
-      <c r="G89" s="3">
-        <v>1500</v>
       </c>
       <c r="H89" s="3">
         <v>1500</v>
       </c>
       <c r="I89" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J89" s="3">
         <v>500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>700</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>4</v>
       </c>
@@ -8066,8 +8282,8 @@
       <c r="U89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
+      <c r="V89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
@@ -8108,8 +8324,11 @@
       <c r="AI89" s="3">
         <v>0</v>
       </c>
+      <c r="AJ89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,34 +8364,35 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-900</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-400</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-300</v>
       </c>
       <c r="L91" s="3">
         <v>-300</v>
@@ -8181,17 +8401,17 @@
         <v>-300</v>
       </c>
       <c r="N91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>4</v>
       </c>
@@ -8204,8 +8424,8 @@
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -8246,8 +8466,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8570,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,53 +8674,56 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-69100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-23300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>4</v>
       </c>
@@ -8507,8 +8736,8 @@
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -8549,8 +8778,11 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,17 +8818,18 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3">
         <v>900</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
@@ -8604,34 +8837,34 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>900</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
       <c r="K96" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="L96" s="3">
         <v>-900</v>
       </c>
       <c r="M96" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="P96" s="3">
         <v>-900</v>
       </c>
       <c r="Q96" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -8687,8 +8920,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9024,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9128,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,53 +9232,56 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3">
         <v>8200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>16100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>21500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>28900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-18600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>42600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2100</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>4</v>
       </c>
@@ -9049,8 +9294,8 @@
       <c r="U100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="V100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -9091,8 +9336,11 @@
       <c r="AI100" s="3">
         <v>0</v>
       </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9117,8 +9365,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9192,53 +9440,56 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>4300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-37200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-23300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-27800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>32800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>4</v>
       </c>
@@ -9251,8 +9502,8 @@
       <c r="U102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
+      <c r="V102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W102" s="3">
         <v>0</v>
@@ -9291,6 +9542,9 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CULL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CULL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="92">
   <si>
     <t>CULL</t>
   </si>
@@ -656,202 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H8" s="3">
+        <v>3900</v>
+      </c>
+      <c r="I8" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J8" s="3">
         <v>4200</v>
       </c>
-      <c r="E8" s="3">
-        <v>4000</v>
-      </c>
-      <c r="F8" s="3">
-        <v>3900</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="K8" s="3">
         <v>4300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="L8" s="3">
         <v>4200</v>
       </c>
-      <c r="I8" s="3">
-        <v>4200</v>
-      </c>
-      <c r="J8" s="3">
-        <v>4300</v>
-      </c>
-      <c r="K8" s="3">
-        <v>4200</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3300</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>4</v>
       </c>
@@ -864,8 +869,8 @@
       <c r="V8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
+      <c r="W8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
@@ -906,8 +911,11 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1010,38 +1018,41 @@
       <c r="AJ9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>3900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J10" s="3">
         <v>4200</v>
       </c>
-      <c r="E10" s="3">
-        <v>4000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>3900</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="K10" s="3">
         <v>4300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="L10" s="3">
         <v>4200</v>
       </c>
-      <c r="I10" s="3">
-        <v>4200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>4300</v>
-      </c>
-      <c r="K10" s="3">
-        <v>4200</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1114,8 +1125,11 @@
       <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1152,8 +1166,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1256,8 +1271,11 @@
       <c r="AJ12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1360,8 +1378,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1371,26 +1392,26 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1464,19 +1485,22 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
         <v>100</v>
@@ -1488,14 +1512,14 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1568,8 +1592,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1603,56 +1630,57 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>3100</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17" s="3">
         <v>3000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2900</v>
       </c>
       <c r="I17" s="3">
         <v>2800</v>
       </c>
       <c r="J17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K17" s="3">
         <v>3200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>300</v>
-      </c>
-      <c r="N17" s="3">
-        <v>400</v>
       </c>
       <c r="O17" s="3">
         <v>400</v>
       </c>
       <c r="P17" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>500</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>4</v>
       </c>
@@ -1665,8 +1693,8 @@
       <c r="V17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
+      <c r="W17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X17" s="3">
         <v>0</v>
@@ -1707,56 +1735,59 @@
       <c r="AJ17" s="3">
         <v>0</v>
       </c>
+      <c r="AK17" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G18" s="3">
         <v>900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1200</v>
       </c>
       <c r="I18" s="3">
         <v>1400</v>
       </c>
       <c r="J18" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K18" s="3">
         <v>1100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2800</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1769,8 +1800,8 @@
       <c r="V18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W18" s="3">
-        <v>0</v>
+      <c r="W18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X18" s="3">
         <v>0</v>
@@ -1811,8 +1842,11 @@
       <c r="AJ18" s="3">
         <v>0</v>
       </c>
+      <c r="AK18" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1849,56 +1883,57 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-4200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-3600</v>
       </c>
       <c r="P20" s="3">
         <v>-3600</v>
       </c>
       <c r="Q20" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1800</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>4</v>
       </c>
@@ -1911,98 +1946,101 @@
       <c r="V20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X20" s="3">
         <v>1200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1100</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>1300</v>
       </c>
       <c r="AB20" s="3">
         <v>1300</v>
       </c>
       <c r="AC20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AD20" s="3">
         <v>1200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1000</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>1100</v>
       </c>
       <c r="AI20" s="3">
         <v>1100</v>
       </c>
       <c r="AJ20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AK20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
         <v>1000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1300</v>
       </c>
       <c r="I21" s="3">
         <v>1500</v>
       </c>
       <c r="J21" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K21" s="3">
         <v>1100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1100</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2057,8 +2095,11 @@
       <c r="AJ21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2086,8 +2127,8 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2161,171 +2202,177 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="3">
         <v>900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>1300</v>
       </c>
       <c r="I23" s="3">
         <v>1400</v>
       </c>
       <c r="J23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K23" s="3">
         <v>1100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1000</v>
-      </c>
-      <c r="V23" s="3">
-        <v>1200</v>
       </c>
       <c r="W23" s="3">
         <v>1200</v>
       </c>
       <c r="X23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y23" s="3">
         <v>1100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1100</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>1300</v>
       </c>
       <c r="AB23" s="3">
         <v>1300</v>
       </c>
       <c r="AC23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AD23" s="3">
         <v>1200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1000</v>
-      </c>
-      <c r="AH23" s="3">
-        <v>1100</v>
       </c>
       <c r="AI23" s="3">
         <v>1100</v>
       </c>
       <c r="AJ23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AK23" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
-      </c>
-      <c r="F24" s="3">
-        <v>200</v>
-      </c>
-      <c r="G24" s="3">
-        <v>300</v>
-      </c>
-      <c r="H24" s="3">
-        <v>300</v>
       </c>
       <c r="I24" s="3">
         <v>300</v>
       </c>
       <c r="J24" s="3">
+        <v>300</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
-      </c>
-      <c r="V24" s="3">
-        <v>300</v>
       </c>
       <c r="W24" s="3">
         <v>300</v>
@@ -2334,34 +2381,34 @@
         <v>300</v>
       </c>
       <c r="Y24" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Z24" s="3">
         <v>200</v>
       </c>
       <c r="AA24" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AB24" s="3">
         <v>300</v>
       </c>
       <c r="AC24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD24" s="3">
         <v>200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>300</v>
-      </c>
-      <c r="AH24" s="3">
-        <v>400</v>
       </c>
       <c r="AI24" s="3">
         <v>400</v>
@@ -2369,8 +2416,11 @@
       <c r="AJ24" s="3">
         <v>400</v>
       </c>
+      <c r="AK24" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2473,56 +2523,59 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>900</v>
-      </c>
-      <c r="E26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26" s="3">
         <v>700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J26" s="3">
-        <v>900</v>
       </c>
       <c r="K26" s="3">
         <v>900</v>
       </c>
       <c r="L26" s="3">
+        <v>900</v>
+      </c>
+      <c r="M26" s="3">
         <v>2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>800</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>4</v>
       </c>
@@ -2535,8 +2588,8 @@
       <c r="V26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
+      <c r="W26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X26" s="3">
         <v>0</v>
@@ -2577,56 +2630,59 @@
       <c r="AJ26" s="3">
         <v>0</v>
       </c>
+      <c r="AK26" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>900</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G27" s="3">
         <v>700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J27" s="3">
-        <v>900</v>
       </c>
       <c r="K27" s="3">
         <v>900</v>
       </c>
       <c r="L27" s="3">
+        <v>900</v>
+      </c>
+      <c r="M27" s="3">
         <v>2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>800</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>4</v>
       </c>
@@ -2639,8 +2695,8 @@
       <c r="V27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
+      <c r="W27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X27" s="3">
         <v>0</v>
@@ -2681,8 +2737,11 @@
       <c r="AJ27" s="3">
         <v>0</v>
       </c>
+      <c r="AK27" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2785,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2889,8 +2951,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2993,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3097,56 +3165,59 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>4200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2300</v>
-      </c>
-      <c r="O32" s="3">
-        <v>3600</v>
       </c>
       <c r="P32" s="3">
         <v>3600</v>
       </c>
       <c r="Q32" s="3">
+        <v>3600</v>
+      </c>
+      <c r="R32" s="3">
         <v>1800</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>4</v>
       </c>
@@ -3159,98 +3230,101 @@
       <c r="V32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X32" s="3">
         <v>-1200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1100</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-1300</v>
       </c>
       <c r="AB32" s="3">
         <v>-1300</v>
       </c>
       <c r="AC32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>-1100</v>
       </c>
       <c r="AI32" s="3">
         <v>-1100</v>
       </c>
       <c r="AJ32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AK32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>900</v>
-      </c>
-      <c r="E33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" s="3">
         <v>700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J33" s="3">
-        <v>900</v>
       </c>
       <c r="K33" s="3">
         <v>900</v>
       </c>
       <c r="L33" s="3">
+        <v>900</v>
+      </c>
+      <c r="M33" s="3">
         <v>2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>800</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>4</v>
       </c>
@@ -3263,8 +3337,8 @@
       <c r="V33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
+      <c r="W33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X33" s="3">
         <v>0</v>
@@ -3305,8 +3379,11 @@
       <c r="AJ33" s="3">
         <v>0</v>
       </c>
+      <c r="AK33" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3409,56 +3486,59 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>900</v>
-      </c>
-      <c r="E35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" s="3">
         <v>700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J35" s="3">
-        <v>900</v>
       </c>
       <c r="K35" s="3">
         <v>900</v>
       </c>
       <c r="L35" s="3">
+        <v>900</v>
+      </c>
+      <c r="M35" s="3">
         <v>2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>800</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>4</v>
       </c>
@@ -3471,8 +3551,8 @@
       <c r="V35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
+      <c r="W35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X35" s="3">
         <v>0</v>
@@ -3513,117 +3593,123 @@
       <c r="AJ35" s="3">
         <v>0</v>
       </c>
+      <c r="AK35" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3660,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3698,56 +3785,57 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>14000</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" s="3">
         <v>17400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>13000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>22800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>26200</v>
       </c>
-      <c r="I41" s="3">
-        <v>27700</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>36600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>28700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3760,8 +3848,8 @@
       <c r="V41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W41" s="3">
-        <v>0</v>
+      <c r="W41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X41" s="3">
         <v>0</v>
@@ -3802,8 +3890,11 @@
       <c r="AJ41" s="3">
         <v>0</v>
       </c>
+      <c r="AK41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3832,26 +3923,26 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>21100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>34900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>59700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>86600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>91200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>53900</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3864,8 +3955,8 @@
       <c r="V42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3906,8 +3997,11 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3935,8 +4029,8 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -4010,8 +4104,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4030,17 +4127,17 @@
       <c r="H44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I44" s="3">
-        <v>100</v>
-      </c>
-      <c r="J44" s="3">
-        <v>100</v>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>100</v>
       </c>
       <c r="L44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4114,25 +4211,28 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3">
         <v>1300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1200</v>
       </c>
       <c r="I45" s="3">
         <v>1100</v>
@@ -4141,11 +4241,11 @@
         <v>1200</v>
       </c>
       <c r="K45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L45" s="3">
         <v>1100</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -4218,38 +4318,41 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>15400</v>
-      </c>
-      <c r="E46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G46" s="3">
         <v>18700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>14300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>23900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>27400</v>
       </c>
-      <c r="I46" s="3">
-        <v>28900</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>37900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>29900</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4322,38 +4425,41 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>23200</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3">
         <v>27700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>28400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>27300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>29400</v>
       </c>
-      <c r="I47" s="3">
-        <v>29800</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>30300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>28600</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -4426,56 +4532,59 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>17100</v>
-      </c>
-      <c r="E48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="3">
         <v>15400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>14000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>12000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>11500</v>
       </c>
-      <c r="I48" s="3">
-        <v>10800</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8500</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4488,8 +4597,8 @@
       <c r="V48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
@@ -4530,19 +4639,22 @@
       <c r="AJ48" s="3">
         <v>0</v>
       </c>
+      <c r="AK48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
+      <c r="D49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G49" s="3">
         <v>0</v>
@@ -4634,8 +4746,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4738,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4842,55 +4960,58 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>13700</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3">
         <v>13100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>13100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>13300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>12900</v>
       </c>
-      <c r="I52" s="3">
-        <v>12900</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1400</v>
-      </c>
-      <c r="P52" s="3">
-        <v>1000</v>
       </c>
       <c r="Q52" s="3">
         <v>1000</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
+      <c r="R52" s="3">
+        <v>1000</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>4</v>
@@ -4904,8 +5025,8 @@
       <c r="V52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
@@ -4946,8 +5067,11 @@
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5050,112 +5174,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>432200</v>
-      </c>
-      <c r="E54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G54" s="3">
         <v>420700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>411600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>417300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>417900</v>
       </c>
-      <c r="I54" s="3">
-        <v>417500</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>423200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>406100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>384000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>353500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>354700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>372600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>376200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>334100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>331400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>326100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>330700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>312500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>298100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>302900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>299500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>299600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>293400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>297200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>301800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>290200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>284200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>282900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>286300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>283900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>274100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>274500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>258800</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5192,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5230,43 +5361,44 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>280800</v>
-      </c>
-      <c r="E57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G57" s="3">
         <v>268400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>269000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>274200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>275200</v>
       </c>
-      <c r="I57" s="3">
-        <v>276500</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>292900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>286800</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
       <c r="N57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O57" s="3">
         <v>100</v>
@@ -5277,8 +5409,8 @@
       <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>4</v>
+      <c r="R57" s="3">
+        <v>100</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>4</v>
@@ -5289,8 +5421,8 @@
       <c r="U57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
+      <c r="V57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
@@ -5334,19 +5466,22 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
@@ -5438,8 +5573,11 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5467,8 +5605,8 @@
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -5497,11 +5635,11 @@
       <c r="U59" s="3">
         <v>0</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W59" s="3">
-        <v>0</v>
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X59" s="3">
         <v>0</v>
@@ -5542,38 +5680,41 @@
       <c r="AJ59" s="3">
         <v>0</v>
       </c>
+      <c r="AK59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>281100</v>
-      </c>
-      <c r="E60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G60" s="3">
         <v>268800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>269200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>274400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>275400</v>
       </c>
-      <c r="I60" s="3">
-        <v>276600</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>293100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>286800</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5646,38 +5787,41 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>45000</v>
       </c>
-      <c r="E61" s="3">
-        <v>45000</v>
-      </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>35100</v>
-      </c>
-      <c r="G61" s="3">
-        <v>35000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>35000</v>
       </c>
       <c r="I61" s="3">
         <v>35000</v>
       </c>
       <c r="J61" s="3">
+        <v>35000</v>
+      </c>
+      <c r="K61" s="3">
         <v>25000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5750,38 +5894,41 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>6400</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3">
         <v>5600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>5600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>6700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>5800</v>
       </c>
-      <c r="I62" s="3">
-        <v>5300</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5800</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -5854,8 +6001,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5958,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6062,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6166,56 +6322,59 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>332500</v>
-      </c>
-      <c r="E66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G66" s="3">
         <v>319400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>309900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>316100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>316100</v>
       </c>
-      <c r="I66" s="3">
-        <v>317000</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>323000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>307600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>285300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>254900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>255000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>273800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>318400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>277500</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>4</v>
       </c>
@@ -6228,8 +6387,8 @@
       <c r="V66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W66" s="3">
-        <v>0</v>
+      <c r="W66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X66" s="3">
         <v>0</v>
@@ -6270,8 +6429,11 @@
       <c r="AJ66" s="3">
         <v>0</v>
       </c>
+      <c r="AK66" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6308,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6412,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6516,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6620,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6724,56 +6896,59 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>62000</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72" s="3">
         <v>59200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>59300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>58500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>57400</v>
       </c>
-      <c r="I72" s="3">
-        <v>56400</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>56600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>55600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>54700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>53400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>53300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>52600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>50500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>49600</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>4</v>
       </c>
@@ -6786,8 +6961,8 @@
       <c r="V72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
+      <c r="W72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X72" s="3">
         <v>0</v>
@@ -6828,8 +7003,11 @@
       <c r="AJ72" s="3">
         <v>0</v>
       </c>
+      <c r="AK72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6932,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7036,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7140,112 +7324,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>99600</v>
-      </c>
-      <c r="E76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G76" s="3">
         <v>101300</v>
-      </c>
-      <c r="F76" s="3">
-        <v>101700</v>
-      </c>
-      <c r="G76" s="3">
-        <v>101200</v>
       </c>
       <c r="H76" s="3">
         <v>101700</v>
       </c>
       <c r="I76" s="3">
-        <v>100600</v>
+        <v>101200</v>
       </c>
       <c r="J76" s="3">
+        <v>101700</v>
+      </c>
+      <c r="K76" s="3">
         <v>100200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>98500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>98700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>98600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>99700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>98800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>57800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>56600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>56900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>55600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>54500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>53000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>53400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>53100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>52200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>51100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>50700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>49400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>48500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>47500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>46900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>45000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>45700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>46000</v>
-      </c>
-      <c r="AH76" s="3">
-        <v>45300</v>
       </c>
       <c r="AI76" s="3">
         <v>45300</v>
       </c>
       <c r="AJ76" s="3">
+        <v>45300</v>
+      </c>
+      <c r="AK76" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7348,165 +7538,171 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>900</v>
-      </c>
-      <c r="E81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G81" s="3">
         <v>700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J81" s="3">
-        <v>900</v>
       </c>
       <c r="K81" s="3">
         <v>900</v>
       </c>
       <c r="L81" s="3">
+        <v>900</v>
+      </c>
+      <c r="M81" s="3">
         <v>2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>800</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>4</v>
       </c>
@@ -7519,8 +7715,8 @@
       <c r="V81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
+      <c r="W81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X81" s="3">
         <v>0</v>
@@ -7561,8 +7757,11 @@
       <c r="AJ81" s="3">
         <v>0</v>
       </c>
+      <c r="AK81" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7599,8 +7798,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7611,13 +7811,13 @@
         <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
@@ -7629,10 +7829,10 @@
         <v>100</v>
       </c>
       <c r="L83" s="3">
+        <v>100</v>
+      </c>
+      <c r="M83" s="3">
         <v>200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
@@ -7641,14 +7841,14 @@
         <v>100</v>
       </c>
       <c r="P83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>4</v>
       </c>
@@ -7661,8 +7861,8 @@
       <c r="V83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -7703,8 +7903,11 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7807,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7911,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8015,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8119,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8223,56 +8438,59 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E89" s="3">
+      <c r="E89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G89" s="3">
         <v>1700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>2400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1500</v>
       </c>
-      <c r="I89" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>700</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>4</v>
       </c>
@@ -8285,8 +8503,8 @@
       <c r="V89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
+      <c r="W89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X89" s="3">
         <v>0</v>
@@ -8327,8 +8545,11 @@
       <c r="AJ89" s="3">
         <v>0</v>
       </c>
+      <c r="AK89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8365,37 +8586,38 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-2100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-300</v>
       </c>
       <c r="M91" s="3">
         <v>-300</v>
@@ -8404,17 +8626,17 @@
         <v>-300</v>
       </c>
       <c r="O91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>4</v>
       </c>
@@ -8427,8 +8649,8 @@
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -8469,8 +8691,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8573,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8677,56 +8905,59 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3">
         <v>-5500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-3300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-3800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1800</v>
       </c>
-      <c r="I94" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-19700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-69100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-23300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5900</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
@@ -8739,8 +8970,8 @@
       <c r="V94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -8781,8 +9012,11 @@
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8819,28 +9053,29 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3">
         <v>900</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -8849,25 +9084,25 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="M96" s="3">
         <v>-900</v>
       </c>
       <c r="N96" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
       <c r="P96" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="Q96" s="3">
         <v>-900</v>
       </c>
       <c r="R96" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
@@ -8923,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9027,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9131,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9235,56 +9479,59 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G100" s="3">
         <v>8200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-6900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1200</v>
       </c>
-      <c r="I100" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>16100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>21500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>28900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-18600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>42600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2100</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>4</v>
       </c>
@@ -9297,8 +9544,8 @@
       <c r="V100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
@@ -9339,8 +9586,11 @@
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
+      <c r="AK100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9368,8 +9618,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9443,8 +9693,11 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9452,47 +9705,47 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>4300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-9800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1500</v>
       </c>
-      <c r="I102" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-37200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-23300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-27800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>32800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3200</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>4</v>
       </c>
@@ -9505,8 +9758,8 @@
       <c r="V102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
+      <c r="W102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X102" s="3">
         <v>0</v>
@@ -9545,6 +9798,9 @@
         <v>0</v>
       </c>
       <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
         <v>0</v>
       </c>
     </row>
